--- a/docs/GRP_SpreadSheet.xlsx
+++ b/docs/GRP_SpreadSheet.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffg\Documents\GitHub\WhenMathPrays\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8111A6E7-7042-4117-B86F-F0A64C57E92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9A1EA7-F364-4185-B3EF-3C7281926D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5772" yWindow="372" windowWidth="11712" windowHeight="13776" xr2:uid="{BDC9F35F-0710-4C80-B890-2C14A82C5ADF}"/>
+    <workbookView xWindow="1248" yWindow="624" windowWidth="19704" windowHeight="12960" activeTab="2" xr2:uid="{BDC9F35F-0710-4C80-B890-2C14A82C5ADF}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
     <sheet name="GRP Equation" sheetId="2" r:id="rId2"/>
+    <sheet name="mapping, Prim-&gt;gamma_self" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
   <si>
     <t>Parameter</t>
   </si>
@@ -85,9 +86,6 @@
   </si>
   <si>
     <t>w_{S,I}</t>
-  </si>
-  <si>
-    <t>Shared silence/presence weight (imaginary axis contribution); tunable, contributes to Love/Hate space.</t>
   </si>
   <si>
     <t>fidelity_scaling_factor</t>
@@ -235,6 +233,108 @@
 B. Entropy targets and rates are axis-independent (Rev 3.4 refinement for timeline independence).
 C. Primitive inputs (v, r, f, a, S) are normalized from human-scale [-10, +10] to [-1, +1] before use (see Equation Sheet for details).
 D. Expected magnitudes (e.g., casual relationships: 5-30) from CONSTANTS.md are not parameters but guidelines; not included here.</t>
+  </si>
+  <si>
+    <t>Shared Breath weight (imaginary axis contribution); tunable, contributes to Love/Hate space.</t>
+  </si>
+  <si>
+    <t>Primitive</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>Real Axis Contribution (to Ego ↔ We)</t>
+  </si>
+  <si>
+    <t>Imaginary Axis Contribution (to Hate ↔ Love)</t>
+  </si>
+  <si>
+    <t>Weight Used</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Visibility</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>w_v = 0.8</t>
+  </si>
+  <si>
+    <t>Measures how much M1 makes themselves visible/available to M2. Contributes directly to the real part of Δγ_self. Higher visibility pulls toward connection ("We" space).</t>
+  </si>
+  <si>
+    <t>Resonance</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>w_r = 1.0</t>
+  </si>
+  <si>
+    <t>Measures how attuned and responsive M1 is emotionally with M2. Contributes directly to the imaginary part of Δγ_self. Higher resonance builds love/affect.</t>
+  </si>
+  <si>
+    <t>Fidelity</t>
+  </si>
+  <si>
+    <t>f (or f' when negative)</t>
+  </si>
+  <si>
+    <t>Altruism</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>w_a = 0.6</t>
+  </si>
+  <si>
+    <t>Measures selfless giving or sacrifice M1 enacts toward M2. Contributes to the imaginary part of Δγ_self. Builds love through care.</t>
+  </si>
+  <si>
+    <t>Shared Silence/Presence (Shared Breath)</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>wv⋅v w_v \cdot v wv​⋅v</t>
+  </si>
+  <si>
+    <t>— (no contribution)</t>
+  </si>
+  <si>
+    <t>wr⋅r w_r \cdot r wr​⋅r</t>
+  </si>
+  <si>
+    <t>wf⋅f′ w_f \cdot f' wf​⋅f′ (where f′=f f' = f f′=f if f ≥ 0, else $$ f' = f \cdot (0.12 \cdot \max(</t>
+  </si>
+  <si>
+    <t>\text{Im}[\gamma_{\text{self}}(n)]</t>
+  </si>
+  <si>
+    <t>, 5.0)) $$)</t>
+  </si>
+  <si>
+    <t>wa⋅a w_a \cdot a wa​⋅a</t>
+  </si>
+  <si>
+    <t>wS,R⋅S w_{S,R} \cdot S wS,R​⋅S</t>
+  </si>
+  <si>
+    <t>wS,I⋅S w_{S,I} \cdot S wS,I​⋅S</t>
+  </si>
+  <si>
+    <t>w_{S,R} = 0.5 (real); w_{S,I} = 0.5 (imag)</t>
+  </si>
+  <si>
+    <t>Measures the felt quality of shared presence or silence as perceived by M1. Unique in contributing to both axes: real for "being there" (connection), imaginary for emotional depth in presence.</t>
   </si>
 </sst>
 </file>
@@ -735,12 +835,12 @@
         <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2">
         <v>0.12</v>
@@ -749,12 +849,12 @@
         <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
@@ -763,40 +863,40 @@
         <v>5</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2">
         <v>0.02</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="2">
         <v>0.02</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2">
         <v>-150</v>
@@ -805,12 +905,12 @@
         <v>5</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
@@ -819,12 +919,12 @@
         <v>5</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="b">
         <v>0</v>
@@ -833,12 +933,12 @@
         <v>5</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -872,114 +972,252 @@
   <sheetData>
     <row r="1" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>63</v>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77447137-0428-4C68-B36E-CC07ACB14791}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="37.109375" customWidth="1"/>
+    <col min="5" max="5" width="27.88671875" customWidth="1"/>
+    <col min="6" max="6" width="69.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/docs/GRP_SpreadSheet.xlsx
+++ b/docs/GRP_SpreadSheet.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffg\Documents\GitHub\WhenMathPrays\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9A1EA7-F364-4185-B3EF-3C7281926D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31E4918-B48C-4567-97DB-74F8320A292A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1248" yWindow="624" windowWidth="19704" windowHeight="12960" activeTab="2" xr2:uid="{BDC9F35F-0710-4C80-B890-2C14A82C5ADF}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="22848" windowHeight="13776" activeTab="1" xr2:uid="{BDC9F35F-0710-4C80-B890-2C14A82C5ADF}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
     <sheet name="GRP Equation" sheetId="2" r:id="rId2"/>
-    <sheet name="mapping, Prim-&gt;gamma_self" sheetId="3" r:id="rId3"/>
+    <sheet name="Primitive-&gt;gamma_self" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="100">
   <si>
     <t>Parameter</t>
   </si>
@@ -148,85 +148,25 @@
     <t>Primitive Normalization</t>
   </si>
   <si>
-    <t>x=human-scale10 x = \frac{\text{human-scale}}{10} x=10human-scale​</t>
-  </si>
-  <si>
-    <t>human-scale ∈ [-10, +10] (from CSV/authoring); x ∈ [-1, +1] (for computation)</t>
-  </si>
-  <si>
-    <t>Prerequisite: Scales inputs (v, r, f, a, S) to computational range. Applies to all primitives before weighting. From CONSTANTS.md (consistent across revisions).</t>
-  </si>
-  <si>
     <t>Fidelity Adjustment (f')</t>
   </si>
   <si>
-    <t>$$ f' = \begin{cases} f \cdot (\text{fidelity_scaling_factor} \cdot \max(</t>
-  </si>
-  <si>
-    <t>\text{Im}[\vec{\gamma}_{\text{self}}(n)]</t>
-  </si>
-  <si>
-    <t>, \text{fidelity_epsilon})) &amp; \text{if } f &lt; 0 \ f &amp; \text{if } f \geq 0 \end{cases} $$</t>
-  </si>
-  <si>
     <t>Real Primitives Delta</t>
   </si>
   <si>
-    <t>δreal=wv⋅v+wS,R⋅S \delta_{\text{real}} = w_v \cdot v + w_{S,R} \cdot S δreal​=wv​⋅v+wS,R​⋅S</t>
-  </si>
-  <si>
     <t>w_v = 0.8; w_{S,R} = 0.5; v and S = normalized primitives</t>
   </si>
   <si>
-    <t>Contribution to real axis (We/Ego space); measures visibility and shared presence from M1's perspective toward M2. Positive moves toward We (positive real).</t>
-  </si>
-  <si>
     <t>Imag Primitives Delta</t>
   </si>
   <si>
-    <t>δimag=wr⋅r+wf⋅f′+wa⋅a+wS,I⋅S \delta_{\text{imag}} = w_r \cdot r + w_f \cdot f' + w_a \cdot a + w_{S,I} \cdot S δimag​=wr​⋅r+wf​⋅f′+wa​⋅a+wS,I​⋅S</t>
-  </si>
-  <si>
-    <t>w_r = 1.0; w_f = 1.2; w_a = 0.6; w_{S,I} = 0.5; r, f' (adjusted), a, S = normalized primitives</t>
-  </si>
-  <si>
-    <t>Contribution to imaginary axis (Love/Hate space); measures resonance, fidelity (adjusted), altruism, and shared presence. Positive moves toward Love (positive imag). f' uses asymmetry for negatives.</t>
-  </si>
-  <si>
     <t>Real Entropy Pull</t>
   </si>
   <si>
-    <t>entropy_pull_real=ΔSreal⋅Δt⋅sign(entropy_real_target−Re[γ⃗self(n)]) \text{entropy\_pull\_real} = \Delta S_{\text{real}} \cdot \Delta t \cdot \text{sign}(\text{entropy\_real\_target} - \text{Re}[\vec{\gamma}_{\text{self}}(n)]) entropy_pull_real=ΔSreal​⋅Δt⋅sign(entropy_real_target−Re[γ​self​(n)])</t>
-  </si>
-  <si>
-    <t>ΔS_real = 0.02; entropy_real_target = -150.0; Re = real part of current γ_self(n); Δt = time elapsed (e.g., days/weeks); sign() = -1, 0, or +1</t>
-  </si>
-  <si>
-    <t>Constant-force entropy on real axis (toward Ego/target). If entropy_per_event = True, omit Δt (fixed per event). New in Rev 3.4 for timeline independence; default pulls leftward to isolation.</t>
-  </si>
-  <si>
     <t>Imag Entropy Pull</t>
   </si>
   <si>
-    <t>entropy_pull_imag=ΔSimag⋅Δt⋅sign(entropy_imag_target−Im[γ⃗self(n)]) \text{entropy\_pull\_imag} = \Delta S_{\text{imag}} \cdot \Delta t \cdot \text{sign}(\text{entropy\_imag\_target} - \text{Im}[\vec{\gamma}_{\text{self}}(n)]) entropy_pull_imag=ΔSimag​⋅Δt⋅sign(entropy_imag_target−Im[γ​self​(n)])</t>
-  </si>
-  <si>
-    <t>ΔS_imag = 0.02; entropy_imag_target = 0.0; Im = imaginary part of current γ_self(n); Δt = time elapsed; sign() = -1, 0, or +1</t>
-  </si>
-  <si>
-    <t>Constant-force entropy on imaginary axis (toward neutral/target). If entropy_per_event = True, omit Δt. New in Rev 3.4; default pulls toward apathy (fades love/hate). Axis-independent from Rev 3.3.</t>
-  </si>
-  <si>
     <t>Overall Position Update</t>
-  </si>
-  <si>
-    <t>γ⃗self(n+1)=γ⃗self(n)+δreal+i⋅δimag+entropy_pull_real+i⋅entropy_pull_imag \vec{\gamma}_{\text{self}}(n+1) = \vec{\gamma}_{\text{self}}(n) + \delta_{\text{real}} + i \cdot \delta_{\text{imag}} + \text{entropy\_pull\_real} + i \cdot \text{entropy\_pull\_imag} γ​self​(n+1)=γ​self​(n)+δreal​+i⋅δimag​+entropy_pull_real+i⋅entropy_pull_imag</t>
-  </si>
-  <si>
-    <t>References all above components; initial γ_self(0) = γ_self0 (baseline, e.g., from temperament; common values like Secure: (1,1))</t>
-  </si>
-  <si>
-    <t>Full recurrence: Evolves position in γ-space (real: Ego/We, imag: Hate/Love). Love = position magnitude (no separate L(t)). Asymmetrical, irreversible; requires positive primitives to counter entropy. Unilateral (M1 about M2).</t>
   </si>
   <si>
     <t>A. All weights (w_*) are defaults and tunable unless locked.
@@ -241,9 +181,6 @@
     <t>Primitive</t>
   </si>
   <si>
-    <t>Symbol</t>
-  </si>
-  <si>
     <t>Real Axis Contribution (to Ego ↔ We)</t>
   </si>
   <si>
@@ -283,9 +220,6 @@
     <t>Fidelity</t>
   </si>
   <si>
-    <t>f (or f' when negative)</t>
-  </si>
-  <si>
     <t>Altruism</t>
   </si>
   <si>
@@ -304,37 +238,118 @@
     <t>S</t>
   </si>
   <si>
-    <t>wv⋅v w_v \cdot v wv​⋅v</t>
-  </si>
-  <si>
     <t>— (no contribution)</t>
   </si>
   <si>
-    <t>wr⋅r w_r \cdot r wr​⋅r</t>
-  </si>
-  <si>
-    <t>wf⋅f′ w_f \cdot f' wf​⋅f′ (where f′=f f' = f f′=f if f ≥ 0, else $$ f' = f \cdot (0.12 \cdot \max(</t>
-  </si>
-  <si>
-    <t>\text{Im}[\gamma_{\text{self}}(n)]</t>
-  </si>
-  <si>
-    <t>, 5.0)) $$)</t>
-  </si>
-  <si>
-    <t>wa⋅a w_a \cdot a wa​⋅a</t>
-  </si>
-  <si>
-    <t>wS,R⋅S w_{S,R} \cdot S wS,R​⋅S</t>
-  </si>
-  <si>
-    <t>wS,I⋅S w_{S,I} \cdot S wS,I​⋅S</t>
-  </si>
-  <si>
-    <t>w_{S,R} = 0.5 (real); w_{S,I} = 0.5 (imag)</t>
-  </si>
-  <si>
     <t>Measures the felt quality of shared presence or silence as perceived by M1. Unique in contributing to both axes: real for "being there" (connection), imaginary for emotional depth in presence.</t>
+  </si>
+  <si>
+    <t>w_v*v</t>
+  </si>
+  <si>
+    <t>w_r*r</t>
+  </si>
+  <si>
+    <t>w_a*a</t>
+  </si>
+  <si>
+    <t>w_(S,R)*S</t>
+  </si>
+  <si>
+    <t>w_(S,I)*S</t>
+  </si>
+  <si>
+    <t>w_{S,R} = 0.5 (real)
+w_{S,I} = 0.5 (imag)</t>
+  </si>
+  <si>
+    <t>Measures faithfulness, reliability, and trust-keeping from M1 toward M2. Has the strongest influence on the Love/Hate axis among all primitives. Positive fidelity builds love steadily using the fixed base weight of 1.2. Negative fidelity (betrayal) is amplified by the current depth of love (|Im[γ_self(n)]|); the deeper the bond, the more a single betrayal hurts. This creates irreversible asymmetry: trust lost is far harder (and often proportionally much more damaging) to rebuild than it was to earn.</t>
+  </si>
+  <si>
+    <t>w_f*f'</t>
+  </si>
+  <si>
+    <t>w_f=1.2*f'; f' is conditional see below:
+if f&gt;=0
+     f'=f 
+Else (if f &lt;0)
+     f'=f*(0.12*max(|Im(gama_self(n)|,5.0))</t>
+  </si>
+  <si>
+    <t>Primitive Symbol</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>w_(S,R)  = real
+w_(S,I)= = imag</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>δ_real = w_v * v + w_{S,R} * S</t>
+  </si>
+  <si>
+    <t>δ_imag = w_r * r + w_f * f' + w_a * a + w_{S,I} * S</t>
+  </si>
+  <si>
+    <t>γ_self(n+1) = γ_self(n) + δ_real + i * δ_imag + entropy_pull_real + i * entropy_pull_imag</t>
+  </si>
+  <si>
+    <t>human-scale in [-10, +10] (from CSV/authoring); results in x in [-1, +1]</t>
+  </si>
+  <si>
+    <t>Asymmetry rule applied only to negative fidelity (betrayal). The impact of negative f is amplified proportionally by the current depth of love/hate (absolute value of the imaginary part); the deeper the bond, the greater the damage from betrayal. Positive fidelity is unchanged (no extra scaling). This creates the core irreversibility: negatives hurt far more than equivalent positives help. LOCKED parameters. Applies only to the f primitive.</t>
+  </si>
+  <si>
+    <t>Contribution to real axis (We/Ego space) from visibility and shared presence. From M1's perspective toward M2. Positive values move toward We (positive real direction).</t>
+  </si>
+  <si>
+    <t>w_r = 1.0; w_f = 1.2; w_a = 0.6; w_{S,I} = 0.5; r, a, S = normalized primitives; f' from Fidelity Adjustment above</t>
+  </si>
+  <si>
+    <t>Contribution to imaginary axis (Love/Hate space) from resonance, fidelity (asymmetrically adjusted via f'), altruism, and shared presence. Positive values move toward Love (positive imaginary direction). Fidelity has the strongest base weight.</t>
+  </si>
+  <si>
+    <t>entropy_pull_real = ΔS_real * Δt * sign(entropy_real_target - Re[γ_self(n)]) (If entropy_per_event = True, omit the * Δt part)</t>
+  </si>
+  <si>
+    <t>ΔS_real = 0.02; entropy_real_target = -150.0; Re = real part of current γ_self(n); Δt = time elapsed; sign() returns -1, 0, or +1</t>
+  </si>
+  <si>
+    <t>Constant-force entropy on real axis (pulls toward Ego/target). Rev 3.4 refinement for timeline independence. Default pulls leftward toward isolation.</t>
+  </si>
+  <si>
+    <t>entropy_pull_imag = ΔS_imag * Δt * sign(entropy_imag_target - Im[γ_self(n)]) (If entropy_per_event = True, omit the * Δt part)</t>
+  </si>
+  <si>
+    <t>ΔS_imag = 0.02; entropy_imag_target = 0.0; Im = imaginary part of current γ_self(n); Δt = time elapsed; sign() returns -1, 0, or +1</t>
+  </si>
+  <si>
+    <t>Constant-force entropy on imaginary axis (pulls toward neutral/target). Rev 3.4 refinement. Axis-independent from real entropy. Default pulls toward emotional apathy.</t>
+  </si>
+  <si>
+    <t>References all components above; initial γ_self(0) = γ_self0 (fixed baseline from temperament/history)</t>
+  </si>
+  <si>
+    <t>Full recurrence equation. Evolves position in complex γ-space (real: Ego → We; imaginary: Hate → Love). Love is the position itself (no separate variable). Requires ongoing positive primitives to overcome entropy. Unilateral (M1 about M2 only). Asymmetrical and irreversible by design.</t>
+  </si>
+  <si>
+    <t>if f &gt;= 0 
+     f' = f 
+else (if f &lt; 0) 
+    f' = f * 0.12 * max( absolute value of imaginary part of γ_self(n) , 5.0 )</t>
+  </si>
+  <si>
+    <t>Prerequisite: Scales inputs (v, r, f, a, S) to computational range, the range of the values per the formulas shown in this table. Applies to all primitives before any weighting. Consistent across revisions.</t>
+  </si>
+  <si>
+    <t>x = human_scale / 10</t>
+  </si>
+  <si>
+    <t>Dependent on value of f &gt;=0 or f&lt;0 and the max(|Im(gamma_self(n)|,5.0).</t>
   </si>
 </sst>
 </file>
@@ -385,7 +400,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -398,6 +413,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -835,7 +853,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -938,7 +956,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -965,12 +983,12 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="2" max="2" width="56.109375" customWidth="1"/>
+    <col min="3" max="3" width="44.33203125" customWidth="1"/>
+    <col min="4" max="4" width="88.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -984,102 +1002,102 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="B8" s="2" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1089,135 +1107,154 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77447137-0428-4C68-B36E-CC07ACB14791}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="37.109375" customWidth="1"/>
-    <col min="5" max="5" width="27.88671875" customWidth="1"/>
-    <col min="6" max="6" width="69.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="37.109375" customWidth="1"/>
+    <col min="6" max="6" width="43.77734375" customWidth="1"/>
+    <col min="7" max="7" width="69.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/docs/GRP_SpreadSheet.xlsx
+++ b/docs/GRP_SpreadSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffg\Documents\GitHub\WhenMathPrays\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31E4918-B48C-4567-97DB-74F8320A292A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB2F569-B90C-458E-A7CD-DB2013384B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="22848" windowHeight="13776" activeTab="1" xr2:uid="{BDC9F35F-0710-4C80-B890-2C14A82C5ADF}"/>
+    <workbookView xWindow="1248" yWindow="624" windowWidth="19704" windowHeight="12960" activeTab="2" xr2:uid="{BDC9F35F-0710-4C80-B890-2C14A82C5ADF}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="102">
   <si>
     <t>Parameter</t>
   </si>
@@ -350,6 +350,12 @@
   </si>
   <si>
     <t>Dependent on value of f &gt;=0 or f&lt;0 and the max(|Im(gamma_self(n)|,5.0).</t>
+  </si>
+  <si>
+    <t>Note: This primitive mapping assumes Human Scale [-10,+10] and not calculation scale [-1,1]</t>
+  </si>
+  <si>
+    <t>Note: the v, r, f, a, S terms in the formula are assume calculation scale [-1,1] except for the Primitive Scale row.</t>
   </si>
 </sst>
 </file>
@@ -400,12 +406,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -414,8 +423,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -955,18 +964,18 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -979,7 +988,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75DB7DB3-CBE9-405C-AF18-FD35638EE700}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" customWidth="1"/>
@@ -1100,14 +1109,25 @@
         <v>95</v>
       </c>
     </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:D9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77447137-0428-4C68-B36E-CC07ACB14791}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
@@ -1152,7 +1172,7 @@
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1178,7 +1198,7 @@
       <c r="D3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1201,13 +1221,13 @@
       <c r="D4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="3" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1224,7 +1244,7 @@
       <c r="D5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1247,7 +1267,7 @@
       <c r="D6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -1257,7 +1277,21 @@
         <v>66</v>
       </c>
     </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:G7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>